--- a/swag-test.xlsx
+++ b/swag-test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ccd3066c8c2526e8/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{758282F5-D809-435D-ACC0-65D46139082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{758282F5-D809-435D-ACC0-65D46139082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CF16644-1455-4B9D-92C1-2B0051B88BA9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{A2A022F2-3D79-4DDF-AFF3-895D953F75F7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
   <si>
     <t>login-001</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,10 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>secret_sauce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不合格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -140,27 +136,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>locked_out_user
-secret_sauce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不合格（锁定用户）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SECRET_SAUCE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不合格（密码多出空格）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>s ecret_sauce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不合格（密码大小写不一样）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,7 +160,46 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不合格（空账号）</t>
+    <t>用户名：standard_user
+密码：secret_sauce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：standard_user
+密码：123456789</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：standard_user
+密码：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：locked_out_user
+密码：secret_sauce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：standard_user
+密码：SECRET_SAUCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：standard_user
+密码：s ecret_sauce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.saucedemo.com/inventory.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：
+密码：secret_sauce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（空用户名）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -185,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +218,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
@@ -219,8 +250,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -229,20 +263,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -561,7 +596,7 @@
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
     <col min="4" max="4" width="8.25" customWidth="1"/>
     <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -593,14 +628,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="34" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -612,8 +647,8 @@
       <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>27</v>
+      <c r="G2" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="H2" t="s">
         <v>23</v>
@@ -622,131 +657,137 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
       <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="4">
-        <v>123456789</v>
+      <c r="F3" s="3"/>
+      <c r="G3" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
       <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="3" t="s">
-        <v>30</v>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
       <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" t="s">
-        <v>32</v>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" t="s">
-        <v>34</v>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H8" t="s">
         <v>23</v>
       </c>
@@ -754,19 +795,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H9" t="s">
         <v>23</v>
       </c>
@@ -774,41 +818,47 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
       <c r="E10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
       <c r="E11" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="1"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="H11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I11" t="s">
         <v>24</v>
@@ -821,6 +871,9 @@
     <mergeCell ref="C2:C11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G10" r:id="rId1" xr:uid="{372C21E4-20B1-4D28-B45C-B68E13BF99D3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/swag-test.xlsx
+++ b/swag-test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ccd3066c8c2526e8/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{758282F5-D809-435D-ACC0-65D46139082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CF16644-1455-4B9D-92C1-2B0051B88BA9}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{758282F5-D809-435D-ACC0-65D46139082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC9A0368-5484-402B-AF4A-9CF8625F16FA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{A2A022F2-3D79-4DDF-AFF3-895D953F75F7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="111">
   <si>
     <t>login-001</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,11 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、输入用户名
-2、输入密码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>登录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,31 +115,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>合格（正确密码）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不合格（错误密码）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不合格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不合格（空密码）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不合格（锁定用户）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不合格（密码多出空格）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不合格（密码大小写不一样）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -181,11 +156,6 @@
   </si>
   <si>
     <t>用户名：standard_user
-密码：SECRET_SAUCE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户名：standard_user
 密码：s ecret_sauce</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,7 +169,337 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不合格（空用户名）</t>
+    <t>login-011</t>
+  </si>
+  <si>
+    <t>login-012</t>
+  </si>
+  <si>
+    <t>login-013</t>
+  </si>
+  <si>
+    <t>login-014</t>
+  </si>
+  <si>
+    <t>login-015</t>
+  </si>
+  <si>
+    <t>login-016</t>
+  </si>
+  <si>
+    <t>login-017</t>
+  </si>
+  <si>
+    <t>login-018</t>
+  </si>
+  <si>
+    <t>login-019</t>
+  </si>
+  <si>
+    <t>login-020</t>
+  </si>
+  <si>
+    <t>合格（正确账号+正确密码）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（正确账号+错误密码）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（正确账号+空密码）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（锁定用户的账号密码）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（密码大小写有误）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（空用户名+正确密码）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（空用户名+空密码）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（用户名多出空格）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：s tandard_user
+密码：secret_sauce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（登录后退出再登录）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（已登录再访问登录页）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（用户名多出特殊字符）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名：s￥tandard_user
+密码：secret_sauce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（复制粘贴密码）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（刷新页面后登录状态）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（多标签页登录）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（登录后浏览器后退）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（退出登录后浏览器后退）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录swag
+网址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、回车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、点击登录
+4、点击左上角菜单
+5、点击登出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、点击登录
+4、点击左上角菜单
+5、点击登出
+6、重复1-3操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、点击登录
+4、开新窗口
+5、输入登录后网址
+6、回车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入登录后网址
+2、回车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、复制密码
+3、粘贴密码
+4、点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、点击登录
+4、刷新页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、开一个新窗口
+2、输入用户名
+3、输入密码
+4、点击登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、点击登录
+4、点击页面左上角后退键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、输入用户名
+2、输入密码
+3、点击登录
+4、点击左上角菜单
+5、点击登出
+6、点击页面左上角后退键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort-002</t>
+  </si>
+  <si>
+    <t>sort-003</t>
+  </si>
+  <si>
+    <t>sort-004</t>
+  </si>
+  <si>
+    <t>sort-005</t>
+  </si>
+  <si>
+    <t>合格（名称A到Z排序）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（名称Z到A排序）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击右上角排序列表
+2、点击“名称A到Z”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击右上角排序列表
+2、点击“名称Z到A”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（价格低到高排序）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击右上角排序列表
+2、点击“价格低到高”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（价格高到低排序）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击右上角排序列表
+2、点击“价格高到低”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（排序后加购物车）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击右上角排序列表
+2、点击“名称Z到A”
+3、点击“加入购物车”
+4、点击购物车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加入购物车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>join-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>join-002</t>
+  </si>
+  <si>
+    <t>join-003</t>
+  </si>
+  <si>
+    <t>join-004</t>
+  </si>
+  <si>
+    <t>join-005</t>
+  </si>
+  <si>
+    <t>合格（单次添加）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击一个“加入购物车”
+2、点击购物车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（多次添加）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击三个“加入购物车”
+2、点击购物车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（添加后移除）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击一个“加入购物车”
+2、点击购物车
+3、点击“删除”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不合格（重复添加）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击一个“加入购物车”
+2、再次点击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合格（刷新页面）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、点击一个“加入购物车”
+2、刷新页面</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -265,14 +565,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -589,14 +889,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F802FB-6B0F-41F2-8E39-1BF4FA722A29}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="27.25" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
     <col min="4" max="4" width="8.25" customWidth="1"/>
     <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.58203125" customWidth="1"/>
+    <col min="7" max="7" width="21.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -633,28 +933,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.3">
@@ -662,22 +962,22 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="3"/>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28" x14ac:dyDescent="0.3">
@@ -685,45 +985,45 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28" x14ac:dyDescent="0.3">
@@ -731,22 +1031,22 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28" x14ac:dyDescent="0.3">
@@ -754,22 +1054,22 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="3"/>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="28" x14ac:dyDescent="0.3">
@@ -777,45 +1077,43 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="C8" s="4"/>
       <c r="D8" s="3"/>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
         <v>23</v>
       </c>
-      <c r="I8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="G9" s="1"/>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="28" x14ac:dyDescent="0.3">
@@ -823,22 +1121,22 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="C10" s="4"/>
       <c r="D10" s="3"/>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="4" t="s">
-        <v>41</v>
+      <c r="G10" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="I10" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28" x14ac:dyDescent="0.3">
@@ -846,33 +1144,512 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="3"/>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3"/>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="3"/>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="126" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="112" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="3"/>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>42</v>
       </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" t="s">
-        <v>24</v>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="3"/>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="3"/>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="3"/>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="126" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="3"/>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="112" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="56" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" t="s">
+        <v>58</v>
+      </c>
+      <c r="I31" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="D2:D11"/>
+  <mergeCells count="6">
+    <mergeCell ref="D22:D31"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="C27:C31"/>
     <mergeCell ref="F2:F11"/>
-    <mergeCell ref="C2:C11"/>
+    <mergeCell ref="C2:C21"/>
+    <mergeCell ref="D2:D21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G10" r:id="rId1" xr:uid="{372C21E4-20B1-4D28-B45C-B68E13BF99D3}"/>
+    <hyperlink ref="G15" r:id="rId1" xr:uid="{372C21E4-20B1-4D28-B45C-B68E13BF99D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
